--- a/smartshop/EvidenceBasedAdaptiveUI/reports/DefaultUI/desktop_defaults.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/DefaultUI/desktop_defaults.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33.5</v>
+        <v>33.04</v>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.5</v>
+        <v>72.77</v>
       </c>
       <c r="D3" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E3" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53.5</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>59.82</v>
       </c>
       <c r="D5" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.5</v>
+        <v>29.02</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43</v>
+        <v>41.96</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42.5</v>
+        <v>41.52</v>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -664,13 +664,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.5</v>
+        <v>26.79</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.5</v>
+        <v>43.75</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E11" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
       <c r="D12" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>47.77</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E13" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>39.29</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
